--- a/artfynd/A 28859-2025 artfynd.xlsx
+++ b/artfynd/A 28859-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125913958</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125913501</v>
       </c>
       <c r="B4" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28859-2025 artfynd.xlsx
+++ b/artfynd/A 28859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,6 +979,123 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126081719</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>506596</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6847072</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Ålind</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Ålind, Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28859-2025 artfynd.xlsx
+++ b/artfynd/A 28859-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125913958</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125913501</v>
       </c>
       <c r="B4" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28859-2025 artfynd.xlsx
+++ b/artfynd/A 28859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1096,6 +1096,307 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126091316</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>506697</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6846976</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126091302</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>506699</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6846972</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126090665</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Guldgruvan, Guldgruvan, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>506938</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6846922</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28859-2025 artfynd.xlsx
+++ b/artfynd/A 28859-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125913958</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125913812</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125913501</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>126081719</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>126091316</v>
       </c>
       <c r="B6" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>126091302</v>
       </c>
       <c r="B7" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>126090665</v>
       </c>
       <c r="B8" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28859-2025 artfynd.xlsx
+++ b/artfynd/A 28859-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125913958</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125913812</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125913501</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>126081719</v>
       </c>
       <c r="B5" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>126091316</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>126091302</v>
       </c>
       <c r="B7" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>126090665</v>
       </c>
       <c r="B8" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28859-2025 artfynd.xlsx
+++ b/artfynd/A 28859-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125913958</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125913812</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125913501</v>
       </c>
       <c r="B4" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>126081719</v>
       </c>
       <c r="B5" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>126091316</v>
       </c>
       <c r="B6" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>126091302</v>
       </c>
       <c r="B7" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>126090665</v>
       </c>
       <c r="B8" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28859-2025 artfynd.xlsx
+++ b/artfynd/A 28859-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125913812</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28859-2025 artfynd.xlsx
+++ b/artfynd/A 28859-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125913812</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28859-2025 artfynd.xlsx
+++ b/artfynd/A 28859-2025 artfynd.xlsx
@@ -1402,7 +1402,7 @@
         <v>134167552</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>134168187</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28859-2025 artfynd.xlsx
+++ b/artfynd/A 28859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>125913958</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -772,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125913812</v>
+        <v>125914012</v>
       </c>
       <c r="B3" t="n">
-        <v>57852</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506656</v>
+        <v>506575</v>
       </c>
       <c r="R3" t="n">
-        <v>6847177</v>
+        <v>6847222</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökande.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,45 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125913501</v>
+        <v>126011409</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506608</v>
+        <v>506554</v>
       </c>
       <c r="R4" t="n">
-        <v>6847090</v>
+        <v>6846964</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt. Växer på Björk.</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,80 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126081719</v>
+        <v>134167552</v>
       </c>
       <c r="B5" t="n">
-        <v>56849</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506596</v>
+        <v>506578</v>
       </c>
       <c r="R5" t="n">
-        <v>6847072</v>
+        <v>6847182</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,44 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Ålind</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Ålind, Thomas Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091316</v>
+        <v>134167659</v>
       </c>
       <c r="B6" t="n">
-        <v>58027</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506697</v>
+        <v>506574</v>
       </c>
       <c r="R6" t="n">
-        <v>6846976</v>
+        <v>6847208</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091302</v>
+        <v>134168187</v>
       </c>
       <c r="B7" t="n">
-        <v>57817</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506699</v>
+        <v>506595</v>
       </c>
       <c r="R7" t="n">
-        <v>6846972</v>
+        <v>6847207</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1260,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,58 +1257,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126090665</v>
+        <v>134168213</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Guldgruvan, Guldgruvan, Hls</t>
+          <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506938</v>
+        <v>506598</v>
       </c>
       <c r="R8" t="n">
-        <v>6846922</v>
+        <v>6847212</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1367,12 +1322,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134167552</v>
+        <v>125913501</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506578</v>
+        <v>506608</v>
       </c>
       <c r="R9" t="n">
-        <v>6847182</v>
+        <v>6847090</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,12 +1424,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt. Växer på Björk.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134168187</v>
+        <v>125913812</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,37 +1472,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506595</v>
+        <v>506656</v>
       </c>
       <c r="R10" t="n">
-        <v>6847207</v>
+        <v>6847177</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,12 +1531,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökande.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,6 +1565,822 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126081719</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>506596</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6847072</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Ålind</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Ålind, Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126090665</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Guldgruvan, Guldgruvan, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>506938</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6846922</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134168231</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>506601</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6847213</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126091316</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>506697</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6846976</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126091302</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>506699</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6846972</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126090638</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Guldgruvan, Guldgruvan, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>506941</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6846925</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fyra individer.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125914740</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>506636</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6846912</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126090566</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Guldgruvan, Guldgruvan, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>506968</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6846932</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28859-2025 artfynd.xlsx
+++ b/artfynd/A 28859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125914012</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126011409</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134167552</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134167659</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125913958</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134168187</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134168213</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125913501</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125913812</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126081719</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090665</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134168231</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091316</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2085,6 +2155,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091302</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090638</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2284,6 +2364,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125914740</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2381,8 +2466,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090566</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>